--- a/data/trans_orig/P57B3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_2023-Estudios-trans_orig.xlsx
@@ -535,7 +535,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según se ha sentido solo/a en 2023</t>
+          <t>Población según se ha sentido solo/a en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -730,12 +730,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32920</t>
+          <t>32135</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53911</t>
+          <t>53873</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -745,12 +745,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,49%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -765,12 +765,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>58362</t>
+          <t>57323</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>81853</t>
+          <t>80686</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -780,12 +780,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,75%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,87%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -800,12 +800,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95420</t>
+          <t>95808</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>129113</t>
+          <t>127385</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,19%</t>
+          <t>10,05%</t>
         </is>
       </c>
     </row>
@@ -843,12 +843,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>44803</t>
+          <t>45020</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70799</t>
+          <t>70269</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -858,12 +858,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,72%</t>
+          <t>8,76%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,77%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -878,12 +878,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>104729</t>
+          <t>106460</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135070</t>
+          <t>135974</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -893,12 +893,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>14,14%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>17,94%</t>
+          <t>18,06%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157081</t>
+          <t>157925</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196618</t>
+          <t>196276</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -928,12 +928,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,4%</t>
+          <t>12,46%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,52%</t>
+          <t>15,49%</t>
         </is>
       </c>
     </row>
@@ -956,12 +956,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>150491</t>
+          <t>150580</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>188478</t>
+          <t>192148</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -971,12 +971,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,27%</t>
+          <t>29,29%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>36,66%</t>
+          <t>37,38%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -991,12 +991,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>266953</t>
+          <t>268975</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>308307</t>
+          <t>310258</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1006,12 +1006,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,45%</t>
+          <t>35,72%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>427091</t>
+          <t>430750</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>485764</t>
+          <t>487205</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1041,12 +1041,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>33,71%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,34%</t>
+          <t>38,45%</t>
         </is>
       </c>
     </row>
@@ -1069,12 +1069,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>224764</t>
+          <t>224607</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>264885</t>
+          <t>268457</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1084,12 +1084,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,72%</t>
+          <t>43,69%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>51,53%</t>
+          <t>52,22%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1104,12 +1104,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>257956</t>
+          <t>256414</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>298356</t>
+          <t>296149</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1119,12 +1119,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,62%</t>
+          <t>39,33%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1139,12 +1139,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>494952</t>
+          <t>493814</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>552344</t>
+          <t>553143</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1154,12 +1154,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>39,06%</t>
+          <t>38,97%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,59%</t>
+          <t>43,66%</t>
         </is>
       </c>
     </row>
@@ -1299,12 +1299,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72057</t>
+          <t>72657</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>908406</t>
+          <t>798467</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1314,12 +1314,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,15%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>39,68%</t>
+          <t>34,88%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1334,12 +1334,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>41818</t>
+          <t>40413</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>74196</t>
+          <t>73889</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1349,12 +1349,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,31%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1369,12 +1369,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>122847</t>
+          <t>126958</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1115568</t>
+          <t>1151178</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1384,12 +1384,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,81%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>25,44%</t>
         </is>
       </c>
     </row>
@@ -1412,12 +1412,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>97828</t>
+          <t>106223</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179575</t>
+          <t>179237</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1427,12 +1427,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1447,12 +1447,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>106231</t>
+          <t>103221</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>175982</t>
+          <t>172305</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1462,12 +1462,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,75%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,71%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1482,12 +1482,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>235673</t>
+          <t>238339</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>339259</t>
+          <t>345091</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1497,12 +1497,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,21%</t>
+          <t>5,27%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,5%</t>
+          <t>7,63%</t>
         </is>
       </c>
     </row>
@@ -1525,12 +1525,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>464906</t>
+          <t>485629</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>780008</t>
+          <t>779415</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1540,12 +1540,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>20,31%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,07%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1560,12 +1560,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>499064</t>
+          <t>491723</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>771234</t>
+          <t>760970</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1575,12 +1575,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>21,99%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,5%</t>
+          <t>34,04%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1595,12 +1595,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1083064</t>
+          <t>1067113</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1497053</t>
+          <t>1503627</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1610,12 +1610,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,94%</t>
+          <t>23,58%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,08%</t>
+          <t>33,23%</t>
         </is>
       </c>
     </row>
@@ -1638,12 +1638,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>815488</t>
+          <t>860775</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1302210</t>
+          <t>1300282</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>35,62%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,88%</t>
+          <t>56,8%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1673,12 +1673,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1235922</t>
+          <t>1250215</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1585838</t>
+          <t>1588719</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1688,12 +1688,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,28%</t>
+          <t>55,92%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>70,93%</t>
+          <t>71,06%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1708,12 +1708,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2119182</t>
+          <t>2112813</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2779716</t>
+          <t>2757352</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1723,12 +1723,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>46,83%</t>
+          <t>46,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>60,94%</t>
         </is>
       </c>
     </row>
@@ -1868,12 +1868,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>6951</t>
+          <t>7245</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21607</t>
+          <t>21524</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1883,12 +1883,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,07%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,34%</t>
+          <t>3,33%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1903,12 +1903,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>7933</t>
+          <t>8026</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>21154</t>
+          <t>20399</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1918,12 +1918,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1938,12 +1938,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18343</t>
+          <t>18024</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36571</t>
+          <t>36425</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1953,12 +1953,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,79%</t>
         </is>
       </c>
     </row>
@@ -1981,12 +1981,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>22422</t>
+          <t>23623</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46235</t>
+          <t>46242</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1996,7 +1996,7 @@
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,65%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2016,12 +2016,12 @@
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29686</t>
+          <t>29744</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>50543</t>
+          <t>49595</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -2031,12 +2031,12 @@
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,52%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2051,12 +2051,12 @@
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>56062</t>
+          <t>57762</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>86861</t>
+          <t>88312</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -2066,12 +2066,12 @@
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>6,76%</t>
         </is>
       </c>
     </row>
@@ -2094,12 +2094,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>156297</t>
+          <t>157315</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>210403</t>
+          <t>212781</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2109,12 +2109,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,17%</t>
+          <t>24,33%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,54%</t>
+          <t>32,91%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2129,12 +2129,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>152944</t>
+          <t>151475</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190979</t>
+          <t>190604</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2144,12 +2144,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>23,18%</t>
+          <t>22,96%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,95%</t>
+          <t>28,89%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2164,12 +2164,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>322467</t>
+          <t>320955</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>389991</t>
+          <t>387932</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2179,12 +2179,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,68%</t>
+          <t>24,57%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>29,7%</t>
         </is>
       </c>
     </row>
@@ -2207,12 +2207,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>388960</t>
+          <t>386624</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>447346</t>
+          <t>443798</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2222,12 +2222,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>60,15%</t>
+          <t>59,79%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>69,18%</t>
+          <t>68,63%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2242,12 +2242,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>414869</t>
+          <t>415678</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>458072</t>
+          <t>458463</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2257,12 +2257,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>62,89%</t>
+          <t>63,01%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,43%</t>
+          <t>69,49%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2277,12 +2277,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>818009</t>
+          <t>822974</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>891050</t>
+          <t>889912</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2292,12 +2292,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>62,62%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,21%</t>
+          <t>68,12%</t>
         </is>
       </c>
     </row>
@@ -2437,12 +2437,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>127982</t>
+          <t>129059</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1045728</t>
+          <t>1142639</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2452,12 +2452,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,71%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>33,12%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2472,12 +2472,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112646</t>
+          <t>112250</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159567</t>
+          <t>159166</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2487,12 +2487,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,36%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2507,12 +2507,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>261441</t>
+          <t>263989</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1333653</t>
+          <t>1453862</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2522,12 +2522,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,68%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>20,48%</t>
         </is>
       </c>
     </row>
@@ -2550,12 +2550,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>181890</t>
+          <t>182533</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>276699</t>
+          <t>274785</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2565,12 +2565,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,29%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2585,12 +2585,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>243788</t>
+          <t>244984</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>337306</t>
+          <t>334947</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2600,12 +2600,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,71%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,25%</t>
+          <t>9,18%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2620,12 +2620,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>468699</t>
+          <t>463307</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>595926</t>
+          <t>596872</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2635,12 +2635,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,53%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,4%</t>
+          <t>8,41%</t>
         </is>
       </c>
     </row>
@@ -2663,12 +2663,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>820088</t>
+          <t>784166</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1135592</t>
+          <t>1133997</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2678,12 +2678,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>23,77%</t>
+          <t>22,73%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,92%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2698,12 +2698,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>924936</t>
+          <t>908583</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1221076</t>
+          <t>1223081</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2713,12 +2713,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>25,35%</t>
+          <t>24,9%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,47%</t>
+          <t>33,52%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2733,12 +2733,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1882489</t>
+          <t>1884483</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2326229</t>
+          <t>2326056</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2748,7 +2748,7 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,52%</t>
+          <t>26,55%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
@@ -2776,12 +2776,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1369757</t>
+          <t>1387024</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1967707</t>
+          <t>1970707</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2791,12 +2791,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>39,7%</t>
+          <t>40,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,04%</t>
+          <t>57,12%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2811,12 +2811,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1951492</t>
+          <t>1951353</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2375658</t>
+          <t>2386228</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,12%</t>
+          <t>65,41%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2846,12 +2846,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3479346</t>
+          <t>3419790</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4148469</t>
+          <t>4155744</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>49,02%</t>
+          <t>48,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,55%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P57B3_2023-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P57B3_2023-Estudios-trans_orig.xlsx
@@ -725,32 +725,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>42433</t>
+          <t>50262</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>32135</t>
+          <t>38112</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53873</t>
+          <t>62512</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>8,25%</t>
+          <t>8,7%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,25%</t>
+          <t>6,6%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -760,32 +760,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>68696</t>
+          <t>78323</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>57323</t>
+          <t>65202</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>80686</t>
+          <t>91637</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,72%</t>
+          <t>11,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -795,32 +795,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>111128</t>
+          <t>128585</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>95808</t>
+          <t>112480</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127385</t>
+          <t>148690</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>8,77%</t>
+          <t>9,2%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>7,56%</t>
+          <t>8,05%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>10,05%</t>
+          <t>10,64%</t>
         </is>
       </c>
     </row>
@@ -838,32 +838,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>56640</t>
+          <t>61675</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>45020</t>
+          <t>48525</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>70269</t>
+          <t>75952</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>8,76%</t>
+          <t>8,4%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>13,67%</t>
+          <t>13,15%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -873,32 +873,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>119083</t>
+          <t>129825</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>106460</t>
+          <t>114742</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>135974</t>
+          <t>147247</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>18,06%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -908,32 +908,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>175723</t>
+          <t>191500</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>157925</t>
+          <t>172431</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>196276</t>
+          <t>212198</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>13,87%</t>
+          <t>13,71%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,34%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>15,49%</t>
+          <t>15,19%</t>
         </is>
       </c>
     </row>
@@ -951,32 +951,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>169650</t>
+          <t>194620</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>150580</t>
+          <t>172911</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>192148</t>
+          <t>218766</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>33,0%</t>
+          <t>33,69%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>29,29%</t>
+          <t>29,94%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>37,38%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -986,32 +986,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>287836</t>
+          <t>310127</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>268975</t>
+          <t>288085</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>310258</t>
+          <t>331178</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,85%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>35,72%</t>
+          <t>35,16%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>40,42%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1021,32 +1021,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>457486</t>
+          <t>504747</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>430750</t>
+          <t>472782</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>487205</t>
+          <t>535395</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,13%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>34,0%</t>
+          <t>33,84%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,33%</t>
         </is>
       </c>
     </row>
@@ -1064,32 +1064,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>245348</t>
+          <t>271045</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>224607</t>
+          <t>248637</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>268457</t>
+          <t>296634</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>47,73%</t>
+          <t>46,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>43,69%</t>
+          <t>43,05%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>52,22%</t>
+          <t>51,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1099,32 +1099,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>277336</t>
+          <t>301071</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>256414</t>
+          <t>279548</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>296149</t>
+          <t>324151</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>36,83%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>39,33%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1134,32 +1134,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>522684</t>
+          <t>572115</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>493814</t>
+          <t>540301</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>553143</t>
+          <t>605437</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>41,25%</t>
+          <t>40,95%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>38,97%</t>
+          <t>38,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,66%</t>
+          <t>43,34%</t>
         </is>
       </c>
     </row>
@@ -1177,17 +1177,17 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>514071</t>
+          <t>577602</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>514071</t>
+          <t>577602</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>514071</t>
+          <t>577602</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1212,17 +1212,17 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>752950</t>
+          <t>819345</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>752950</t>
+          <t>819345</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>752950</t>
+          <t>819345</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1247,17 +1247,17 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>1267021</t>
+          <t>1396947</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>1267021</t>
+          <t>1396947</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>1267021</t>
+          <t>1396947</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1294,32 +1294,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>315025</t>
+          <t>83863</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>72657</t>
+          <t>65908</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>798467</t>
+          <t>103135</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>13,76%</t>
+          <t>3,76%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>3,17%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>34,88%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1329,32 +1329,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>56435</t>
+          <t>67563</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>40413</t>
+          <t>55480</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>73889</t>
+          <t>84076</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,88%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1364,32 +1364,32 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>371460</t>
+          <t>151425</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>126958</t>
+          <t>129232</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>1151178</t>
+          <t>175456</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>8,21%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>25,44%</t>
+          <t>3,99%</t>
         </is>
       </c>
     </row>
@@ -1407,32 +1407,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>149625</t>
+          <t>166250</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>106223</t>
+          <t>141376</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>179237</t>
+          <t>190405</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>4,64%</t>
+          <t>6,34%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,54%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1442,32 +1442,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>144884</t>
+          <t>171671</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>103221</t>
+          <t>148676</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>172305</t>
+          <t>196682</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>7,91%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>6,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>7,71%</t>
+          <t>9,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1477,32 +1477,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>294508</t>
+          <t>337922</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>238339</t>
+          <t>305928</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>345091</t>
+          <t>373657</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>6,51%</t>
+          <t>7,68%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>6,96%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -1520,32 +1520,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>678014</t>
+          <t>748330</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>485629</t>
+          <t>699220</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>779415</t>
+          <t>801795</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>29,62%</t>
+          <t>33,57%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>31,36%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>35,96%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1555,32 +1555,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>669537</t>
+          <t>751451</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>491723</t>
+          <t>710640</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>760970</t>
+          <t>790885</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>29,95%</t>
+          <t>34,64%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>21,99%</t>
+          <t>32,76%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>34,04%</t>
+          <t>36,46%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1590,32 +1590,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>1347551</t>
+          <t>1499781</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1067113</t>
+          <t>1435779</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>1503627</t>
+          <t>1567340</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>29,78%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>23,58%</t>
+          <t>32,64%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>33,23%</t>
+          <t>35,63%</t>
         </is>
       </c>
     </row>
@@ -1633,32 +1633,32 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>1146637</t>
+          <t>1230969</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>860775</t>
+          <t>1174792</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>1300282</t>
+          <t>1287318</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>50,09%</t>
+          <t>55,21%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>52,7%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>56,8%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1668,32 +1668,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>1364824</t>
+          <t>1178346</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1250215</t>
+          <t>1135365</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>1588719</t>
+          <t>1220720</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>61,05%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>55,92%</t>
+          <t>52,34%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>71,06%</t>
+          <t>56,28%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1703,32 +1703,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>2511461</t>
+          <t>2409315</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2112813</t>
+          <t>2338720</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>2757352</t>
+          <t>2482408</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>55,5%</t>
+          <t>54,78%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>46,69%</t>
+          <t>53,17%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>60,94%</t>
+          <t>56,44%</t>
         </is>
       </c>
     </row>
@@ -1746,17 +1746,17 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>2289301</t>
+          <t>2229412</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2289301</t>
+          <t>2229412</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>2289301</t>
+          <t>2229412</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>2235679</t>
+          <t>2169031</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2235679</t>
+          <t>2169031</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>2235679</t>
+          <t>2169031</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1816,17 +1816,17 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>4524980</t>
+          <t>4398443</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>4524980</t>
+          <t>4398443</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>4524980</t>
+          <t>4398443</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1863,32 +1863,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>12716</t>
+          <t>14056</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>7245</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>21524</t>
+          <t>24032</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>1,12%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>3,33%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1898,32 +1898,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>13056</t>
+          <t>14665</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>8026</t>
+          <t>9028</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>20399</t>
+          <t>22166</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>1,98%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>1,22%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1933,32 +1933,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>25772</t>
+          <t>28721</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>18024</t>
+          <t>20665</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>36425</t>
+          <t>40684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,81%</t>
         </is>
       </c>
     </row>
@@ -1976,32 +1976,32 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>32896</t>
+          <t>40934</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>23623</t>
+          <t>30149</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>46242</t>
+          <t>55323</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>5,09%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>3,65%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,77%</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
@@ -2011,32 +2011,32 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>38338</t>
+          <t>42760</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>29744</t>
+          <t>32568</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>49595</t>
+          <t>54492</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,82%</t>
         </is>
       </c>
       <c r="O15" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="P15" s="2" t="inlineStr">
         <is>
-          <t>7,52%</t>
+          <t>7,42%</t>
         </is>
       </c>
       <c r="Q15" s="2" t="inlineStr">
@@ -2046,32 +2046,32 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>71233</t>
+          <t>83694</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>57762</t>
+          <t>68104</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>88312</t>
+          <t>103805</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
         <is>
-          <t>5,45%</t>
+          <t>5,79%</t>
         </is>
       </c>
       <c r="V15" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W15" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -2089,32 +2089,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>182108</t>
+          <t>195151</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>157315</t>
+          <t>170705</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>212781</t>
+          <t>222641</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>28,16%</t>
+          <t>27,42%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>24,33%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>32,91%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2124,32 +2124,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>170183</t>
+          <t>190278</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>151475</t>
+          <t>170498</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>190604</t>
+          <t>209389</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>25,8%</t>
+          <t>25,92%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>22,96%</t>
+          <t>23,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>28,89%</t>
+          <t>28,52%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2159,32 +2159,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>352292</t>
+          <t>385429</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>320955</t>
+          <t>353891</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>387932</t>
+          <t>418319</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>26,97%</t>
+          <t>26,66%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>24,57%</t>
+          <t>24,48%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>29,7%</t>
+          <t>28,93%</t>
         </is>
       </c>
     </row>
@@ -2202,32 +2202,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>418903</t>
+          <t>461447</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>386624</t>
+          <t>433593</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>443798</t>
+          <t>486765</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>64,78%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>59,79%</t>
+          <t>60,93%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>68,63%</t>
+          <t>68,41%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2237,32 +2237,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>438147</t>
+          <t>486428</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>415678</t>
+          <t>465416</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>458463</t>
+          <t>510525</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>63,01%</t>
+          <t>63,4%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>69,49%</t>
+          <t>69,54%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2272,22 +2272,22 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>857051</t>
+          <t>947875</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>822974</t>
+          <t>910799</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>889912</t>
+          <t>984326</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>65,61%</t>
+          <t>65,56%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
@@ -2297,7 +2297,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,09%</t>
         </is>
       </c>
     </row>
@@ -2315,17 +2315,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>646623</t>
+          <t>711587</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2350,17 +2350,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>659724</t>
+          <t>734131</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>659724</t>
+          <t>734131</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>659724</t>
+          <t>734131</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2385,17 +2385,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>1306348</t>
+          <t>1445719</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>1306348</t>
+          <t>1445719</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>1306348</t>
+          <t>1445719</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2432,32 +2432,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>370173</t>
+          <t>148181</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>129059</t>
+          <t>125151</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>1142639</t>
+          <t>171997</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>10,73%</t>
+          <t>4,21%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>33,12%</t>
+          <t>4,89%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2467,32 +2467,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>138186</t>
+          <t>160551</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>112250</t>
+          <t>142558</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>159166</t>
+          <t>182372</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,31%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,83%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>4,36%</t>
+          <t>4,9%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2502,32 +2502,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>508360</t>
+          <t>308731</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>263989</t>
+          <t>281845</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>1453862</t>
+          <t>345013</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>20,48%</t>
+          <t>4,76%</t>
         </is>
       </c>
     </row>
@@ -2545,32 +2545,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>239160</t>
+          <t>268859</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>182533</t>
+          <t>234806</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>274785</t>
+          <t>302488</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2580,32 +2580,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>302304</t>
+          <t>344256</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>244984</t>
+          <t>314084</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>334947</t>
+          <t>377505</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>8,29%</t>
+          <t>9,25%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,71%</t>
+          <t>8,44%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>9,18%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2615,32 +2615,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>541464</t>
+          <t>613115</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>463307</t>
+          <t>570612</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>596872</t>
+          <t>664305</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>7,63%</t>
+          <t>8,47%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>7,88%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>9,17%</t>
         </is>
       </c>
     </row>
@@ -2658,32 +2658,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>1029773</t>
+          <t>1138101</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>784166</t>
+          <t>1074783</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>1133997</t>
+          <t>1194542</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>29,85%</t>
+          <t>32,35%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>22,73%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>32,87%</t>
+          <t>33,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2693,32 +2693,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>1127555</t>
+          <t>1251856</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>908583</t>
+          <t>1202957</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>1223081</t>
+          <t>1306113</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>30,91%</t>
+          <t>33,63%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>32,32%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>33,52%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2728,32 +2728,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>2157329</t>
+          <t>2389957</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>1884483</t>
+          <t>2311381</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>2326056</t>
+          <t>2471675</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>30,39%</t>
+          <t>33,01%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>26,55%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>32,77%</t>
+          <t>34,13%</t>
         </is>
       </c>
     </row>
@@ -2771,32 +2771,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>1810889</t>
+          <t>1963460</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1387024</t>
+          <t>1899327</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>1970707</t>
+          <t>2032265</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>52,49%</t>
+          <t>55,8%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>40,2%</t>
+          <t>53,98%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>57,12%</t>
+          <t>57,76%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2806,32 +2806,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2080307</t>
+          <t>1965845</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1951353</t>
+          <t>1909033</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>2386228</t>
+          <t>2020135</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>57,02%</t>
+          <t>52,81%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>53,49%</t>
+          <t>51,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>54,27%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>3891195</t>
+          <t>3929304</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3419790</t>
+          <t>3840706</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>4155744</t>
+          <t>4009543</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>54,82%</t>
+          <t>54,26%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>48,18%</t>
+          <t>53,04%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>58,55%</t>
+          <t>55,37%</t>
         </is>
       </c>
     </row>
@@ -2884,17 +2884,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>3449996</t>
+          <t>3518601</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>3449996</t>
+          <t>3518601</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>3449996</t>
+          <t>3518601</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,17 +2919,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>3648352</t>
+          <t>3722508</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>3648352</t>
+          <t>3722508</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>3648352</t>
+          <t>3722508</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2954,17 +2954,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>7098348</t>
+          <t>7241108</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7098348</t>
+          <t>7241108</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>7098348</t>
+          <t>7241108</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
